--- a/artfynd/A 6417-2025 artfynd.xlsx
+++ b/artfynd/A 6417-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131735176</v>
+        <v>122743513</v>
       </c>
       <c r="B2" t="n">
-        <v>99098</v>
+        <v>80382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Näveråsen Ö, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545400</v>
+        <v>545507</v>
       </c>
       <c r="R2" t="n">
-        <v>6839484</v>
+        <v>6839660</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>150</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Hellström</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -785,49 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131735094</v>
+        <v>122743514</v>
       </c>
       <c r="B3" t="n">
-        <v>99098</v>
+        <v>80382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Näveråsen Ö, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545407</v>
+        <v>545502</v>
       </c>
       <c r="R3" t="n">
-        <v>6839447</v>
+        <v>6839661</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,17 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>150</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Hellström</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -895,49 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131735156</v>
+        <v>122743516</v>
       </c>
       <c r="B4" t="n">
-        <v>99098</v>
+        <v>80382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Näveråsen Ö, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545417</v>
+        <v>545494</v>
       </c>
       <c r="R4" t="n">
-        <v>6839400</v>
+        <v>6839669</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,17 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>175</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,7 +967,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peter Hellström</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1005,49 +978,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131735169</v>
+        <v>122743512</v>
       </c>
       <c r="B5" t="n">
-        <v>99098</v>
+        <v>80488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gräningen Nordost, Hls</t>
+          <t>Näveråsen Ö, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545358</v>
+        <v>545519</v>
       </c>
       <c r="R5" t="n">
-        <v>6839686</v>
+        <v>6839651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,17 +1043,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,7 +1073,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peter Hellström</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1115,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131735191</v>
+        <v>131735083</v>
       </c>
       <c r="B6" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,19 +1114,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>175</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Gatvattnet Sydväst, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545409</v>
+        <v>545067</v>
       </c>
       <c r="R6" t="n">
-        <v>6839481</v>
+        <v>6839709</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,17 +1153,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131735174</v>
+        <v>131735084</v>
       </c>
       <c r="B7" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,19 +1224,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>175</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Gatvattnet Sydväst, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545412</v>
+        <v>545068</v>
       </c>
       <c r="R7" t="n">
-        <v>6839453</v>
+        <v>6839731</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,17 +1263,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,10 +1304,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131735180</v>
+        <v>131735085</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,19 +1334,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Gräningen Öst, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545394</v>
+        <v>545418</v>
       </c>
       <c r="R8" t="n">
-        <v>6839474</v>
+        <v>6839698</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,17 +1373,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131735184</v>
+        <v>131735086</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,19 +1444,19 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Gräningen Öst, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545399</v>
+        <v>545466</v>
       </c>
       <c r="R9" t="n">
-        <v>6839478</v>
+        <v>6839709</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,17 +1483,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131735161</v>
+        <v>131735087</v>
       </c>
       <c r="B10" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,14 +1559,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Gräningen Öst, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545237</v>
+        <v>545417</v>
       </c>
       <c r="R10" t="n">
-        <v>6839538</v>
+        <v>6839705</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,12 +1593,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1665,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131735175</v>
+        <v>131735088</v>
       </c>
       <c r="B11" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,19 +1664,19 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Sydväst, Hls</t>
+          <t>Gräningen Öst, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545601</v>
+        <v>545464</v>
       </c>
       <c r="R11" t="n">
-        <v>6839342</v>
+        <v>6839696</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,17 +1703,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,7 +1747,7 @@
         <v>131735090</v>
       </c>
       <c r="B12" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131735164</v>
+        <v>131735091</v>
       </c>
       <c r="B13" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,19 +1884,19 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>300</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gräningen Nordost, Hls</t>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545324</v>
+        <v>545402</v>
       </c>
       <c r="R13" t="n">
-        <v>6839732</v>
+        <v>6839415</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,17 +1923,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>300</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1995,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131735168</v>
+        <v>131735092</v>
       </c>
       <c r="B14" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,19 +1994,19 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gräningen Nordost, Hls</t>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545367</v>
+        <v>545372</v>
       </c>
       <c r="R14" t="n">
-        <v>6839697</v>
+        <v>6839458</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,17 +2033,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131735159</v>
+        <v>131735093</v>
       </c>
       <c r="B15" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2144,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545259</v>
+        <v>545379</v>
       </c>
       <c r="R15" t="n">
-        <v>6839288</v>
+        <v>6839468</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,12 +2143,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2215,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131735085</v>
+        <v>131735094</v>
       </c>
       <c r="B16" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,19 +2214,19 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gräningen Öst, Hls</t>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545418</v>
+        <v>545407</v>
       </c>
       <c r="R16" t="n">
-        <v>6839698</v>
+        <v>6839447</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,7 +2263,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,7 +2297,7 @@
         <v>131735095</v>
       </c>
       <c r="B17" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,10 +2404,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131735196</v>
+        <v>131735096</v>
       </c>
       <c r="B18" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,7 +2434,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2474,10 +2443,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545421</v>
+        <v>545426</v>
       </c>
       <c r="R18" t="n">
-        <v>6839481</v>
+        <v>6839500</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,17 +2473,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131735181</v>
+        <v>131735097</v>
       </c>
       <c r="B19" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2575,7 +2544,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2584,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545403</v>
+        <v>545435</v>
       </c>
       <c r="R19" t="n">
-        <v>6839457</v>
+        <v>6839501</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,17 +2583,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2655,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131735151</v>
+        <v>131735098</v>
       </c>
       <c r="B20" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,19 +2654,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Sydväst, Hls</t>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545475</v>
+        <v>545425</v>
       </c>
       <c r="R20" t="n">
-        <v>6839374</v>
+        <v>6839496</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2724,17 +2693,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,10 +2734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131735155</v>
+        <v>131735099</v>
       </c>
       <c r="B21" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2795,7 +2764,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>170</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2804,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545395</v>
+        <v>545427</v>
       </c>
       <c r="R21" t="n">
-        <v>6839425</v>
+        <v>6839489</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,17 +2803,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2875,10 +2844,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131735182</v>
+        <v>131735100</v>
       </c>
       <c r="B22" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2905,7 +2874,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>300</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2914,10 +2883,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545401</v>
+        <v>545389</v>
       </c>
       <c r="R22" t="n">
-        <v>6839475</v>
+        <v>6839495</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2944,17 +2913,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>300</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2985,10 +2954,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131735091</v>
+        <v>131735148</v>
       </c>
       <c r="B23" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3015,7 +2984,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3024,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545402</v>
+        <v>545417</v>
       </c>
       <c r="R23" t="n">
-        <v>6839415</v>
+        <v>6839490</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3054,17 +3023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3095,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131735097</v>
+        <v>131735149</v>
       </c>
       <c r="B24" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3125,7 +3094,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3134,10 +3103,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545435</v>
+        <v>545430</v>
       </c>
       <c r="R24" t="n">
-        <v>6839501</v>
+        <v>6839474</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3164,17 +3133,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3208,7 +3177,7 @@
         <v>131735150</v>
       </c>
       <c r="B25" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,10 +3284,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131735160</v>
+        <v>131735151</v>
       </c>
       <c r="B26" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,19 +3314,19 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Stora Ljusvallshatten Sydväst, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545274</v>
+        <v>545475</v>
       </c>
       <c r="R26" t="n">
-        <v>6839560</v>
+        <v>6839374</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3384,17 +3353,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3425,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131735188</v>
+        <v>131735152</v>
       </c>
       <c r="B27" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3455,7 +3424,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3464,10 +3433,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545418</v>
+        <v>545416</v>
       </c>
       <c r="R27" t="n">
-        <v>6839466</v>
+        <v>6839441</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3494,17 +3463,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3535,10 +3504,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131735192</v>
+        <v>131735153</v>
       </c>
       <c r="B28" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3565,7 +3534,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3574,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545408</v>
+        <v>545400</v>
       </c>
       <c r="R28" t="n">
-        <v>6839476</v>
+        <v>6839449</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3604,17 +3573,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3645,10 +3614,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131735167</v>
+        <v>131735155</v>
       </c>
       <c r="B29" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3675,19 +3644,19 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gräningen Öst, Hls</t>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545374</v>
+        <v>545395</v>
       </c>
       <c r="R29" t="n">
-        <v>6839699</v>
+        <v>6839425</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3714,17 +3683,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3755,10 +3724,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131735083</v>
+        <v>131735156</v>
       </c>
       <c r="B30" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3790,14 +3759,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gatvattnet Sydväst, Hls</t>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545067</v>
+        <v>545417</v>
       </c>
       <c r="R30" t="n">
-        <v>6839709</v>
+        <v>6839400</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3824,12 +3793,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3865,10 +3834,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131735171</v>
+        <v>131735157</v>
       </c>
       <c r="B31" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3895,19 +3864,19 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Stora Ljusvallshatten Sydväst, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545318</v>
+        <v>545559</v>
       </c>
       <c r="R31" t="n">
-        <v>6839444</v>
+        <v>6839319</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3934,17 +3903,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3975,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131735163</v>
+        <v>131735158</v>
       </c>
       <c r="B32" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4005,19 +3974,19 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gräningen Nordost, Hls</t>
+          <t>Stora Ljusvallshatten Sydväst, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545306</v>
+        <v>545556</v>
       </c>
       <c r="R32" t="n">
-        <v>6839716</v>
+        <v>6839276</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4044,17 +4013,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4085,10 +4054,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131735172</v>
+        <v>131735159</v>
       </c>
       <c r="B33" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,10 +4093,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545339</v>
+        <v>545259</v>
       </c>
       <c r="R33" t="n">
-        <v>6839439</v>
+        <v>6839288</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,12 +4123,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4195,10 +4164,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131735190</v>
+        <v>131735160</v>
       </c>
       <c r="B34" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4225,7 +4194,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4234,10 +4203,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545410</v>
+        <v>545274</v>
       </c>
       <c r="R34" t="n">
-        <v>6839480</v>
+        <v>6839560</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4274,7 +4243,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4305,10 +4274,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131735186</v>
+        <v>131735161</v>
       </c>
       <c r="B35" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4335,7 +4304,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4344,10 +4313,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>545413</v>
+        <v>545237</v>
       </c>
       <c r="R35" t="n">
-        <v>6839462</v>
+        <v>6839538</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4384,7 +4353,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4415,10 +4384,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131735185</v>
+        <v>131735163</v>
       </c>
       <c r="B36" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4445,19 +4414,19 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Gräningen Nordost, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545407</v>
+        <v>545306</v>
       </c>
       <c r="R36" t="n">
-        <v>6839469</v>
+        <v>6839716</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4494,7 +4463,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4525,10 +4494,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131735197</v>
+        <v>131735164</v>
       </c>
       <c r="B37" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4555,19 +4524,19 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Gräningen Nordost, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545416</v>
+        <v>545324</v>
       </c>
       <c r="R37" t="n">
-        <v>6839481</v>
+        <v>6839732</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4604,7 +4573,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4635,10 +4604,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131735194</v>
+        <v>131735165</v>
       </c>
       <c r="B38" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4665,19 +4634,19 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Gräningen Nordost, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545410</v>
+        <v>545373</v>
       </c>
       <c r="R38" t="n">
-        <v>6839481</v>
+        <v>6839739</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4714,7 +4683,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4745,10 +4714,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131735165</v>
+        <v>131735166</v>
       </c>
       <c r="B39" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4775,19 +4744,19 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gräningen Nordost, Hls</t>
+          <t>Gräningen Öst, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>545373</v>
+        <v>545393</v>
       </c>
       <c r="R39" t="n">
-        <v>6839739</v>
+        <v>6839720</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4824,7 +4793,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4855,10 +4824,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131735093</v>
+        <v>131735167</v>
       </c>
       <c r="B40" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4885,19 +4854,19 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Gräningen Öst, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>545379</v>
+        <v>545374</v>
       </c>
       <c r="R40" t="n">
-        <v>6839468</v>
+        <v>6839699</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4924,17 +4893,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4965,10 +4934,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131735157</v>
+        <v>131735168</v>
       </c>
       <c r="B41" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4995,19 +4964,19 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Sydväst, Hls</t>
+          <t>Gräningen Nordost, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>545559</v>
+        <v>545367</v>
       </c>
       <c r="R41" t="n">
-        <v>6839319</v>
+        <v>6839697</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5034,17 +5003,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5075,10 +5044,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131735149</v>
+        <v>131735169</v>
       </c>
       <c r="B42" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5105,19 +5074,19 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Gräningen Nordost, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545430</v>
+        <v>545358</v>
       </c>
       <c r="R42" t="n">
-        <v>6839474</v>
+        <v>6839686</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5144,17 +5113,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5185,10 +5154,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131735183</v>
+        <v>131735170</v>
       </c>
       <c r="B43" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5215,19 +5184,19 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Väst, Hls</t>
+          <t>Gräningen Öst, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>545393</v>
+        <v>545367</v>
       </c>
       <c r="R43" t="n">
-        <v>6839472</v>
+        <v>6839666</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5264,7 +5233,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5295,10 +5264,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131735148</v>
+        <v>131735171</v>
       </c>
       <c r="B44" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5325,7 +5294,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5334,10 +5303,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>545417</v>
+        <v>545318</v>
       </c>
       <c r="R44" t="n">
-        <v>6839490</v>
+        <v>6839444</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5364,17 +5333,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5405,10 +5374,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131735158</v>
+        <v>131735172</v>
       </c>
       <c r="B45" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5435,19 +5404,19 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stora Ljusvallshatten Sydväst, Hls</t>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>545556</v>
+        <v>545339</v>
       </c>
       <c r="R45" t="n">
-        <v>6839276</v>
+        <v>6839439</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5474,17 +5443,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5515,10 +5484,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131735153</v>
+        <v>131735173</v>
       </c>
       <c r="B46" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5545,7 +5514,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5554,10 +5523,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>545400</v>
+        <v>545420</v>
       </c>
       <c r="R46" t="n">
-        <v>6839449</v>
+        <v>6839455</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5584,17 +5553,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>500</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5625,10 +5594,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131735096</v>
+        <v>131735174</v>
       </c>
       <c r="B47" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5655,7 +5624,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5664,10 +5633,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>545426</v>
+        <v>545412</v>
       </c>
       <c r="R47" t="n">
-        <v>6839500</v>
+        <v>6839453</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5694,17 +5663,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5735,10 +5704,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131735166</v>
+        <v>131735175</v>
       </c>
       <c r="B48" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5765,19 +5734,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gräningen Öst, Hls</t>
+          <t>Stora Ljusvallshatten Sydväst, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>545393</v>
+        <v>545601</v>
       </c>
       <c r="R48" t="n">
-        <v>6839720</v>
+        <v>6839342</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5814,7 +5783,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5845,10 +5814,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131735178</v>
+        <v>131735176</v>
       </c>
       <c r="B49" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5875,7 +5844,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5884,10 +5853,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>545394</v>
+        <v>545400</v>
       </c>
       <c r="R49" t="n">
-        <v>6839480</v>
+        <v>6839484</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5924,7 +5893,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5955,10 +5924,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131735092</v>
+        <v>131735178</v>
       </c>
       <c r="B50" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5985,7 +5954,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5994,10 +5963,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>545372</v>
+        <v>545394</v>
       </c>
       <c r="R50" t="n">
-        <v>6839458</v>
+        <v>6839480</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6024,17 +5993,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6065,10 +6034,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131735195</v>
+        <v>131735180</v>
       </c>
       <c r="B51" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6095,7 +6064,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6104,10 +6073,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>545418</v>
+        <v>545394</v>
       </c>
       <c r="R51" t="n">
-        <v>6839481</v>
+        <v>6839474</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6144,7 +6113,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6175,10 +6144,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131735170</v>
+        <v>131735181</v>
       </c>
       <c r="B52" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6205,19 +6174,19 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gräningen Öst, Hls</t>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>545367</v>
+        <v>545403</v>
       </c>
       <c r="R52" t="n">
-        <v>6839666</v>
+        <v>6839457</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6254,7 +6223,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6285,10 +6254,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131735100</v>
+        <v>131735182</v>
       </c>
       <c r="B53" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6315,7 +6284,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6324,10 +6293,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>545389</v>
+        <v>545401</v>
       </c>
       <c r="R53" t="n">
-        <v>6839495</v>
+        <v>6839475</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6354,17 +6323,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6395,10 +6364,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131735152</v>
+        <v>131735183</v>
       </c>
       <c r="B54" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6425,7 +6394,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6434,10 +6403,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>545416</v>
+        <v>545393</v>
       </c>
       <c r="R54" t="n">
-        <v>6839441</v>
+        <v>6839472</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6464,17 +6433,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6505,10 +6474,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131735173</v>
+        <v>131735184</v>
       </c>
       <c r="B55" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6535,7 +6504,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6544,10 +6513,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>545420</v>
+        <v>545399</v>
       </c>
       <c r="R55" t="n">
-        <v>6839455</v>
+        <v>6839478</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6584,7 +6553,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6615,10 +6584,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131735187</v>
+        <v>131735185</v>
       </c>
       <c r="B56" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6645,7 +6614,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6654,10 +6623,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>545416</v>
+        <v>545407</v>
       </c>
       <c r="R56" t="n">
-        <v>6839464</v>
+        <v>6839469</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6694,7 +6663,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6725,10 +6694,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131735193</v>
+        <v>131735186</v>
       </c>
       <c r="B57" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6755,7 +6724,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6767,7 +6736,7 @@
         <v>545413</v>
       </c>
       <c r="R57" t="n">
-        <v>6839487</v>
+        <v>6839462</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6804,7 +6773,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6835,45 +6804,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131734300</v>
+        <v>131735187</v>
       </c>
       <c r="B58" t="n">
-        <v>92312</v>
+        <v>99195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6040186</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stora Ljusvallshatten Väst, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>545413</v>
+        <v>545416</v>
       </c>
       <c r="R58" t="n">
-        <v>6839439</v>
+        <v>6839464</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6900,12 +6873,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6914,7 +6892,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6937,10 +6914,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131735098</v>
+        <v>131735188</v>
       </c>
       <c r="B59" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6967,7 +6944,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6976,10 +6953,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>545425</v>
+        <v>545418</v>
       </c>
       <c r="R59" t="n">
-        <v>6839496</v>
+        <v>6839466</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7006,17 +6983,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7047,10 +7024,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131735099</v>
+        <v>131735190</v>
       </c>
       <c r="B60" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7077,7 +7054,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7086,10 +7063,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>545427</v>
+        <v>545410</v>
       </c>
       <c r="R60" t="n">
-        <v>6839489</v>
+        <v>6839480</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7116,17 +7093,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7157,10 +7134,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131735084</v>
+        <v>131735191</v>
       </c>
       <c r="B61" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7187,19 +7164,19 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gatvattnet Sydväst, Hls</t>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>545068</v>
+        <v>545409</v>
       </c>
       <c r="R61" t="n">
-        <v>6839731</v>
+        <v>6839481</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7226,17 +7203,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7260,6 +7237,869 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131735192</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>545408</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6839476</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Peter Hellström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>131735193</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>545413</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6839487</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Peter Hellström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>131735194</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>545410</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6839481</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Peter Hellström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>131735195</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>545418</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6839481</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Peter Hellström</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>131735196</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>545421</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6839481</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Peter Hellström</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>131735197</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>545416</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6839481</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Peter Hellström</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>122743515</v>
+      </c>
+      <c r="B68" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Näveråsen Ö, Hls</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>545505</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6839658</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>131734300</v>
+      </c>
+      <c r="B69" t="n">
+        <v>92366</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Stora Ljusvallshatten Väst, Hls</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>545413</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6839439</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Peter Hellström</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 6417-2025 artfynd.xlsx
+++ b/artfynd/A 6417-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743513</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743514</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743516</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743512</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735083</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735084</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735085</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1521,6 +1561,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735086</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,6 +1676,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735087</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735088</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1851,6 +1906,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735090</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735091</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2071,6 +2136,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735092</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2181,6 +2251,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735093</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2291,6 +2366,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735094</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2401,6 +2481,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735095</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2511,6 +2596,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735096</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2621,6 +2711,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735097</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2731,6 +2826,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735098</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2841,6 +2941,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735099</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2951,6 +3056,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735100</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3061,6 +3171,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735148</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3171,6 +3286,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735149</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3281,6 +3401,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735150</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3391,6 +3516,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735151</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3501,6 +3631,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735152</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3611,6 +3746,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735153</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3721,6 +3861,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735155</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3831,6 +3976,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735156</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3941,6 +4091,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735157</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4051,6 +4206,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735158</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4161,6 +4321,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735159</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4271,6 +4436,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735160</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4381,6 +4551,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735161</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4491,6 +4666,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735163</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4601,6 +4781,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735164</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4711,6 +4896,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735165</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4821,6 +5011,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735166</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4931,6 +5126,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735167</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5041,6 +5241,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735168</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5151,6 +5356,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735169</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5261,6 +5471,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735170</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5371,6 +5586,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735171</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5481,6 +5701,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735172</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5591,6 +5816,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735173</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5701,6 +5931,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735174</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5811,6 +6046,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735175</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5921,6 +6161,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735176</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6031,6 +6276,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735178</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6141,6 +6391,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735180</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6251,6 +6506,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735181</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6361,6 +6621,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735182</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6471,6 +6736,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735183</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6581,6 +6851,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735184</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6691,6 +6966,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735185</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6801,6 +7081,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735186</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6911,6 +7196,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735187</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7021,6 +7311,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735188</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7131,6 +7426,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735190</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7241,6 +7541,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735191</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7351,6 +7656,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735192</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7461,6 +7771,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735193</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7571,6 +7886,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735194</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7681,6 +8001,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735195</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7791,6 +8116,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735196</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7901,6 +8231,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735197</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8002,6 +8337,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743515</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8104,8 +8444,83 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734300</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>